--- a/Danh_Sach_Xe.xlsx
+++ b/Danh_Sach_Xe.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="231">
   <si>
     <t>DANH SÁCH CBCNV ĐĂNG KÝ CHO THUÊ PHƯƠNG TIỆN CÁ NHÂN (XE MÔ TÔ) PHỤC VỤ SXKD</t>
   </si>
@@ -706,6 +706,12 @@
   </si>
   <si>
     <t>Phát quang, phát điện dự phòng, PCCC</t>
+  </si>
+  <si>
+    <t>Lương Nguyễn Khôi Nguyên</t>
+  </si>
+  <si>
+    <t>66B3-123.89</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" customWidth="1"/>
@@ -1183,7 +1189,7 @@
     </row>
     <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <f t="shared" ref="A6:A65" si="0">A5+1</f>
+        <f t="shared" ref="A6:A66" si="0">A5+1</f>
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -1461,23 +1467,23 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>64</v>
+      <c r="B17" s="4">
+        <v>34339</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>65</v>
+        <v>229</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>66</v>
+        <v>230</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="H17" s="1"/>
     </row>
@@ -1487,10 +1493,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>20</v>
@@ -1499,10 +1505,10 @@
         <v>16</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H18" s="1"/>
     </row>
@@ -1512,22 +1518,22 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H19" s="1"/>
     </row>
@@ -1537,22 +1543,22 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H20" s="1"/>
     </row>
@@ -1562,22 +1568,22 @@
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="H21" s="1"/>
     </row>
@@ -1587,22 +1593,22 @@
         <v>19</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="H22" s="1"/>
     </row>
@@ -1612,22 +1618,22 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="H23" s="1"/>
     </row>
@@ -1637,22 +1643,22 @@
         <v>21</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="H24" s="1"/>
     </row>
@@ -1662,19 +1668,19 @@
         <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>96</v>
@@ -1687,19 +1693,19 @@
         <v>23</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>96</v>
@@ -1712,19 +1718,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G27" s="4" t="s">
         <v>96</v>
@@ -1737,19 +1743,19 @@
         <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>96</v>
@@ -1762,22 +1768,22 @@
         <v>26</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="H29" s="1"/>
     </row>
@@ -1787,19 +1793,19 @@
         <v>27</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G30" s="4" t="s">
         <v>71</v>
@@ -1812,22 +1818,22 @@
         <v>28</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="H31" s="1"/>
     </row>
@@ -1837,22 +1843,22 @@
         <v>29</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="H32" s="1"/>
     </row>
@@ -1862,22 +1868,22 @@
         <v>30</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="H33" s="1"/>
     </row>
@@ -1887,22 +1893,22 @@
         <v>31</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="H34" s="1"/>
     </row>
@@ -1912,22 +1918,22 @@
         <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="H35" s="1"/>
     </row>
@@ -1937,22 +1943,22 @@
         <v>33</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="H36" s="1"/>
     </row>
@@ -1962,22 +1968,22 @@
         <v>34</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="H37" s="1"/>
     </row>
@@ -1987,22 +1993,22 @@
         <v>35</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="H38" s="1"/>
     </row>
@@ -2012,22 +2018,22 @@
         <v>36</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="H39" s="1"/>
     </row>
@@ -2037,19 +2043,19 @@
         <v>37</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>96</v>
@@ -2062,22 +2068,22 @@
         <v>38</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="H41" s="1"/>
     </row>
@@ -2087,19 +2093,19 @@
         <v>39</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>21</v>
+        <v>157</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>67</v>
@@ -2112,10 +2118,10 @@
         <v>40</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>20</v>
@@ -2124,10 +2130,10 @@
         <v>21</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="H43" s="1"/>
     </row>
@@ -2137,22 +2143,22 @@
         <v>41</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="H44" s="1"/>
     </row>
@@ -2162,22 +2168,22 @@
         <v>42</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="H45" s="1"/>
     </row>
@@ -2187,22 +2193,22 @@
         <v>43</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="H46" s="1"/>
     </row>
@@ -2212,19 +2218,19 @@
         <v>44</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>71</v>
@@ -2237,19 +2243,19 @@
         <v>45</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>71</v>
@@ -2262,19 +2268,19 @@
         <v>46</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>185</v>
+        <v>16</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>71</v>
@@ -2287,19 +2293,19 @@
         <v>47</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>71</v>
@@ -2312,19 +2318,19 @@
         <v>48</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>192</v>
+        <v>111</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>71</v>
@@ -2337,22 +2343,22 @@
         <v>49</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="H52" s="1"/>
     </row>
@@ -2362,22 +2368,22 @@
         <v>50</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>199</v>
+        <v>21</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="H53" s="1"/>
     </row>
@@ -2387,22 +2393,22 @@
         <v>51</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>16</v>
+        <v>199</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="H54" s="1"/>
     </row>
@@ -2412,22 +2418,22 @@
         <v>52</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>206</v>
+        <v>16</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>208</v>
+        <v>29</v>
       </c>
       <c r="H55" s="1"/>
     </row>
@@ -2437,22 +2443,22 @@
         <v>53</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>21</v>
+        <v>206</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>71</v>
+        <v>208</v>
       </c>
       <c r="H56" s="1"/>
     </row>
@@ -2461,19 +2467,23 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B57" s="4"/>
+      <c r="B57" s="4" t="s">
+        <v>209</v>
+      </c>
       <c r="C57" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4">
-        <v>0</v>
+        <v>20</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>213</v>
+        <v>71</v>
       </c>
       <c r="H57" s="1"/>
     </row>
@@ -2484,17 +2494,17 @@
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E58" s="4"/>
-      <c r="F58" s="4" t="s">
-        <v>215</v>
+      <c r="F58" s="4">
+        <v>0</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>71</v>
+        <v>213</v>
       </c>
       <c r="H58" s="1"/>
     </row>
@@ -2505,14 +2515,14 @@
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E59" s="4"/>
-      <c r="F59" s="4">
-        <v>0</v>
+      <c r="F59" s="4" t="s">
+        <v>215</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>71</v>
@@ -2526,17 +2536,17 @@
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4">
         <v>0</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="H60" s="1"/>
     </row>
@@ -2547,17 +2557,17 @@
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E61" s="4"/>
-      <c r="F61" s="4" t="s">
-        <v>219</v>
+      <c r="F61" s="4">
+        <v>0</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>220</v>
+        <v>29</v>
       </c>
       <c r="H61" s="1"/>
     </row>
@@ -2568,14 +2578,14 @@
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E62" s="4"/>
       <c r="F62" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>220</v>
@@ -2589,14 +2599,14 @@
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E63" s="4"/>
       <c r="F63" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>220</v>
@@ -2610,14 +2620,14 @@
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E64" s="4"/>
       <c r="F64" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>220</v>
@@ -2631,28 +2641,39 @@
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="H65" s="1"/>
+    </row>
+    <row r="66" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="4">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4">
+      <c r="D66" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4">
         <v>0</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="G66" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="H65" s="1"/>
-    </row>
-    <row r="66" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
       <c r="H66" s="1"/>
     </row>
     <row r="67" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
@@ -2675,6 +2696,16 @@
       <c r="G68" s="6"/>
       <c r="H68" s="1"/>
     </row>
+    <row r="69" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
